--- a/tools/importer/reports/import-landing-overview.report.xlsx
+++ b/tools/importer/reports/import-landing-overview.report.xlsx
@@ -73,7 +73,7 @@
     <t>landing-overview</t>
   </si>
   <si>
-    <t>2026-08-06T15:52:53.715Z</t>
+    <t>2026-08-06T20:31:22.310Z</t>
   </si>
   <si>
     <t>About Us</t>
@@ -127,13 +127,13 @@
     <t>us/en/magazine.report.json</t>
   </si>
   <si>
-    <t>["columns-featured","cards-teaser","cards-teaser","cards-teaser"]</t>
+    <t>["columns-featured","cards-teaser"]</t>
   </si>
   <si>
     <t>us/en/magazine</t>
   </si>
   <si>
-    <t>2026-08-06T14:52:03.498Z</t>
+    <t>2026-08-06T20:31:17.047Z</t>
   </si>
   <si>
     <t>Magazine</t>
@@ -154,7 +154,7 @@
     <t>adventure-detail</t>
   </si>
   <si>
-    <t>2026-08-06T12:47:09.084Z</t>
+    <t>2026-08-06T20:18:32.550Z</t>
   </si>
   <si>
     <t>Bali Surf Camp</t>
@@ -169,7 +169,7 @@
     <t>us/en/adventures/beervana-portland</t>
   </si>
   <si>
-    <t>2026-08-06T12:47:14.457Z</t>
+    <t>2026-08-06T20:18:37.526Z</t>
   </si>
   <si>
     <t>Beervana in Portland</t>
@@ -184,7 +184,7 @@
     <t>us/en/adventures/climbing-new-zealand</t>
   </si>
   <si>
-    <t>2026-08-06T12:47:19.050Z</t>
+    <t>2026-08-06T20:18:42.235Z</t>
   </si>
   <si>
     <t>Climbing New Zealand</t>
@@ -199,7 +199,7 @@
     <t>us/en/adventures/colorado-rock-climbing</t>
   </si>
   <si>
-    <t>2026-08-06T12:47:26.002Z</t>
+    <t>2026-08-06T20:18:47.811Z</t>
   </si>
   <si>
     <t>Colorado Rock Climbing</t>
@@ -214,7 +214,7 @@
     <t>us/en/adventures/cycling-southern-utah</t>
   </si>
   <si>
-    <t>2026-08-06T12:47:32.025Z</t>
+    <t>2026-08-06T20:18:52.812Z</t>
   </si>
   <si>
     <t>Cycling Southern Utah</t>
@@ -229,7 +229,7 @@
     <t>us/en/adventures/cycling-tuscany</t>
   </si>
   <si>
-    <t>2026-08-06T12:47:37.148Z</t>
+    <t>2026-08-06T20:18:58.625Z</t>
   </si>
   <si>
     <t>Cycling Tuscany</t>
@@ -244,7 +244,7 @@
     <t>us/en/adventures/downhill-skiing-wyoming</t>
   </si>
   <si>
-    <t>2026-08-06T12:47:41.220Z</t>
+    <t>2026-08-06T20:19:04.749Z</t>
   </si>
   <si>
     <t>Downhill Skiing Wyoming</t>
@@ -259,7 +259,7 @@
     <t>us/en/adventures/gastronomic-marais-tour</t>
   </si>
   <si>
-    <t>2026-08-06T12:47:46.408Z</t>
+    <t>2026-08-06T20:19:10.090Z</t>
   </si>
   <si>
     <t>Gastronomic Marais Tour</t>
@@ -274,7 +274,7 @@
     <t>us/en/adventures/napa-wine-tasting</t>
   </si>
   <si>
-    <t>2026-08-06T12:47:51.637Z</t>
+    <t>2026-08-06T20:19:14.880Z</t>
   </si>
   <si>
     <t>Napa Wine Tasting</t>
@@ -289,7 +289,7 @@
     <t>us/en/adventures/riverside-camping-australia</t>
   </si>
   <si>
-    <t>2026-08-06T12:47:57.968Z</t>
+    <t>2026-08-06T20:19:20.728Z</t>
   </si>
   <si>
     <t>Riverside Camping</t>
@@ -304,7 +304,7 @@
     <t>us/en/adventures/ski-touring-mont-blanc</t>
   </si>
   <si>
-    <t>2026-08-06T12:48:02.619Z</t>
+    <t>2026-08-06T20:19:26.685Z</t>
   </si>
   <si>
     <t>Ski Touring Mont Blanc</t>
@@ -319,7 +319,7 @@
     <t>us/en/adventures/surf-camp-costa-rica</t>
   </si>
   <si>
-    <t>2026-08-06T12:48:08.905Z</t>
+    <t>2026-08-06T20:19:32.841Z</t>
   </si>
   <si>
     <t>Surf Camp in Costa Rica</t>
@@ -334,7 +334,7 @@
     <t>us/en/adventures/tahoe-skiing</t>
   </si>
   <si>
-    <t>2026-08-06T12:48:14.122Z</t>
+    <t>2026-08-06T20:19:36.507Z</t>
   </si>
   <si>
     <t>Tahoe Skiing</t>
@@ -349,7 +349,7 @@
     <t>us/en/adventures/west-coast-cycling</t>
   </si>
   <si>
-    <t>2026-08-06T12:48:20.326Z</t>
+    <t>2026-08-06T20:19:42.543Z</t>
   </si>
   <si>
     <t>West Coast Cycling</t>
@@ -364,7 +364,7 @@
     <t>us/en/adventures/whistler-mountain-biking</t>
   </si>
   <si>
-    <t>2026-08-06T12:48:25.700Z</t>
+    <t>2026-08-06T20:19:48.103Z</t>
   </si>
   <si>
     <t>Whistler Mountain Biking</t>
@@ -379,7 +379,7 @@
     <t>us/en/adventures/yosemite-backpacking</t>
   </si>
   <si>
-    <t>2026-08-06T12:48:31.485Z</t>
+    <t>2026-08-06T20:19:53.543Z</t>
   </si>
   <si>
     <t>Yosemite Backpacking</t>

--- a/tools/importer/reports/import-landing-overview.report.xlsx
+++ b/tools/importer/reports/import-landing-overview.report.xlsx
@@ -52,7 +52,7 @@
     <t>homepage</t>
   </si>
   <si>
-    <t>2026-08-06T07:12:15.609Z</t>
+    <t>2026-08-06T22:38:34.867Z</t>
   </si>
   <si>
     <t>WKND Adventures and Travel</t>
@@ -73,7 +73,7 @@
     <t>landing-overview</t>
   </si>
   <si>
-    <t>2026-08-06T20:31:22.310Z</t>
+    <t>2026-08-07T04:07:19.057Z</t>
   </si>
   <si>
     <t>About Us</t>
@@ -94,7 +94,7 @@
     <t>adventures-listing</t>
   </si>
   <si>
-    <t>2026-08-06T14:19:44.390Z</t>
+    <t>2026-08-07T04:06:25.537Z</t>
   </si>
   <si>
     <t>Adventures</t>
@@ -133,7 +133,7 @@
     <t>us/en/magazine</t>
   </si>
   <si>
-    <t>2026-08-06T20:31:17.047Z</t>
+    <t>2026-08-07T04:07:14.284Z</t>
   </si>
   <si>
     <t>Magazine</t>
